--- a/table/Datas/#CharacterLoadout.xlsx
+++ b/table/Datas/#CharacterLoadout.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,10 +476,6 @@
           <t>##group</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -509,7 +505,6 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>1</t>
@@ -532,7 +527,6 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>2</t>
@@ -555,7 +549,6 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>3</t>
@@ -578,7 +571,6 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>4</t>
@@ -601,7 +593,6 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
           <t>5</t>
@@ -624,7 +615,6 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
           <t>6</t>
@@ -647,7 +637,6 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
           <t>7</t>
@@ -670,7 +659,6 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
           <t>8</t>
@@ -693,7 +681,6 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
           <t>9</t>
@@ -716,7 +703,6 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
           <t>10</t>
@@ -735,6 +721,52 @@
       <c r="E14" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>monster_001</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>monster_002</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
